--- a/Structure_Data/text.9.14/20260914_198/structure_factor_20260914_198.xlsx
+++ b/Structure_Data/text.9.14/20260914_198/structure_factor_20260914_198.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D366"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3802 @@
         <v>14.4404860855204</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.445514678955078</v>
+      </c>
+      <c r="C30">
+        <v>0.445133209228516</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.445514678955078</v>
+      </c>
+      <c r="C31">
+        <v>0.445133209228516</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.403121948242188</v>
+      </c>
+      <c r="C32">
+        <v>0.395675659179688</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.310649871826172</v>
+      </c>
+      <c r="C33">
+        <v>0.274749755859375</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.274196624755859</v>
+      </c>
+      <c r="C34">
+        <v>0.217987060546875</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.253150939941406</v>
+      </c>
+      <c r="C35">
+        <v>0.139289855957031</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.165946960449219</v>
+      </c>
+      <c r="C36">
+        <v>0.0551643371582031</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.126190185546875</v>
+      </c>
+      <c r="C37">
+        <v>0.0269355773925781</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.113269805908203</v>
+      </c>
+      <c r="C38">
+        <v>0.0155792236328125</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.0701065063476562</v>
+      </c>
+      <c r="C39">
+        <v>0.0115928649902344</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0573921203613281</v>
+      </c>
+      <c r="C40">
+        <v>0.0103034973144531</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.0480804443359375</v>
+      </c>
+      <c r="C41">
+        <v>0.00654220581054688</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0441360473632812</v>
+      </c>
+      <c r="C42">
+        <v>0.006683349609375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.0341873168945312</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>0.0196037292480469</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B45">
+        <v>0.0151405334472656</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B46">
+        <v>0.011138916015625</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B47">
+        <v>0.0067596435546875</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B48">
+        <v>0.00528335571289062</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B49">
+        <v>0.00349044799804688</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B50">
+        <v>0.002960205078125</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2.5</v>
+      </c>
+      <c r="B51">
+        <v>0.00260543823242188</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>23575</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>2.476967126193</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>2.31264212563299</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.05</v>
+      </c>
+      <c r="B68">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.1</v>
+      </c>
+      <c r="B69">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.15</v>
+      </c>
+      <c r="B70">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.2</v>
+      </c>
+      <c r="B71">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.25</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.3</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.35</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.4</v>
+      </c>
+      <c r="B75">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.45</v>
+      </c>
+      <c r="B76">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.5</v>
+      </c>
+      <c r="B77">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.55</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.6</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.65</v>
+      </c>
+      <c r="B80">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.7</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.75</v>
+      </c>
+      <c r="B82">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.85</v>
+      </c>
+      <c r="B84">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.9</v>
+      </c>
+      <c r="B85">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.95</v>
+      </c>
+      <c r="B86">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.5</v>
+      </c>
+      <c r="B88">
+        <v>5122</v>
+      </c>
+      <c r="C88">
+        <v>0.217264050901379</v>
+      </c>
+      <c r="D88">
+        <v>0.217264050901379</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>1</v>
+      </c>
+      <c r="B89">
+        <v>3939</v>
+      </c>
+      <c r="C89">
+        <v>0.167083775185578</v>
+      </c>
+      <c r="D89">
+        <v>0.384347826086957</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>1.5</v>
+      </c>
+      <c r="B90">
+        <v>2908</v>
+      </c>
+      <c r="C90">
+        <v>0.123351007423118</v>
+      </c>
+      <c r="D90">
+        <v>0.507698833510074</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>2</v>
+      </c>
+      <c r="B91">
+        <v>2378</v>
+      </c>
+      <c r="C91">
+        <v>0.100869565217391</v>
+      </c>
+      <c r="D91">
+        <v>0.608568398727465</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>2.5</v>
+      </c>
+      <c r="B92">
+        <v>1701</v>
+      </c>
+      <c r="C92">
+        <v>0.072152704135737</v>
+      </c>
+      <c r="D92">
+        <v>0.680721102863203</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="B93">
+        <v>1399</v>
+      </c>
+      <c r="C93">
+        <v>0.0593425238600212</v>
+      </c>
+      <c r="D93">
+        <v>0.740063626723224</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>3.5</v>
+      </c>
+      <c r="B94">
+        <v>1192</v>
+      </c>
+      <c r="C94">
+        <v>0.0505620360551432</v>
+      </c>
+      <c r="D94">
+        <v>0.790625662778367</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95">
+        <v>965</v>
+      </c>
+      <c r="C95">
+        <v>0.0409331919406151</v>
+      </c>
+      <c r="D95">
+        <v>0.831558854718982</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>4.5</v>
+      </c>
+      <c r="B96">
+        <v>722</v>
+      </c>
+      <c r="C96">
+        <v>0.0306256627783669</v>
+      </c>
+      <c r="D96">
+        <v>0.862184517497349</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97">
+        <v>668</v>
+      </c>
+      <c r="C97">
+        <v>0.0283351007423118</v>
+      </c>
+      <c r="D97">
+        <v>0.890519618239661</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>5.5</v>
+      </c>
+      <c r="B98">
+        <v>525</v>
+      </c>
+      <c r="C98">
+        <v>0.0222693531283139</v>
+      </c>
+      <c r="D98">
+        <v>0.912788971367975</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>6</v>
+      </c>
+      <c r="B99">
+        <v>375</v>
+      </c>
+      <c r="C99">
+        <v>0.0159066808059385</v>
+      </c>
+      <c r="D99">
+        <v>0.928695652173913</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>6.5</v>
+      </c>
+      <c r="B100">
+        <v>318</v>
+      </c>
+      <c r="C100">
+        <v>0.0134888653234358</v>
+      </c>
+      <c r="D100">
+        <v>0.942184517497349</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>7</v>
+      </c>
+      <c r="B101">
+        <v>229</v>
+      </c>
+      <c r="C101">
+        <v>0.00971367974549311</v>
+      </c>
+      <c r="D101">
+        <v>0.951898197242842</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>7.5</v>
+      </c>
+      <c r="B102">
+        <v>189</v>
+      </c>
+      <c r="C102">
+        <v>0.008016967126193</v>
+      </c>
+      <c r="D102">
+        <v>0.959915164369035</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103">
+        <v>186</v>
+      </c>
+      <c r="C103">
+        <v>0.00788971367974549</v>
+      </c>
+      <c r="D103">
+        <v>0.96780487804878</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>8.5</v>
+      </c>
+      <c r="B104">
+        <v>150</v>
+      </c>
+      <c r="C104">
+        <v>0.0063626723223754</v>
+      </c>
+      <c r="D104">
+        <v>0.974167550371156</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>9</v>
+      </c>
+      <c r="B105">
+        <v>119</v>
+      </c>
+      <c r="C105">
+        <v>0.00504772004241782</v>
+      </c>
+      <c r="D105">
+        <v>0.979215270413574</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>9.5</v>
+      </c>
+      <c r="B106">
+        <v>98</v>
+      </c>
+      <c r="C106">
+        <v>0.00415694591728526</v>
+      </c>
+      <c r="D106">
+        <v>0.983372216330859</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>10</v>
+      </c>
+      <c r="B107">
+        <v>69</v>
+      </c>
+      <c r="C107">
+        <v>0.00292682926829268</v>
+      </c>
+      <c r="D107">
+        <v>0.986299045599152</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>10.5</v>
+      </c>
+      <c r="B108">
+        <v>66</v>
+      </c>
+      <c r="C108">
+        <v>0.00279957582184518</v>
+      </c>
+      <c r="D108">
+        <v>0.989098621420997</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>11</v>
+      </c>
+      <c r="B109">
+        <v>62</v>
+      </c>
+      <c r="C109">
+        <v>0.00262990455991516</v>
+      </c>
+      <c r="D109">
+        <v>0.991728525980912</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>11.5</v>
+      </c>
+      <c r="B110">
+        <v>38</v>
+      </c>
+      <c r="C110">
+        <v>0.0016118769883351</v>
+      </c>
+      <c r="D110">
+        <v>0.993340402969247</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>12</v>
+      </c>
+      <c r="B111">
+        <v>31</v>
+      </c>
+      <c r="C111">
+        <v>0.00131495227995758</v>
+      </c>
+      <c r="D111">
+        <v>0.994655355249205</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>12.5</v>
+      </c>
+      <c r="B112">
+        <v>33</v>
+      </c>
+      <c r="C112">
+        <v>0.00139978791092259</v>
+      </c>
+      <c r="D112">
+        <v>0.996055143160127</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>13</v>
+      </c>
+      <c r="B113">
+        <v>20</v>
+      </c>
+      <c r="C113">
+        <v>0.000848356309650053</v>
+      </c>
+      <c r="D113">
+        <v>0.996903499469777</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>13.5</v>
+      </c>
+      <c r="B114">
+        <v>13</v>
+      </c>
+      <c r="C114">
+        <v>0.000551431601272534</v>
+      </c>
+      <c r="D114">
+        <v>0.99745493107105</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>14</v>
+      </c>
+      <c r="B115">
+        <v>12</v>
+      </c>
+      <c r="C115">
+        <v>0.000509013785790032</v>
+      </c>
+      <c r="D115">
+        <v>0.99796394485684</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>14.5</v>
+      </c>
+      <c r="B116">
+        <v>12</v>
+      </c>
+      <c r="C116">
+        <v>0.000509013785790032</v>
+      </c>
+      <c r="D116">
+        <v>0.99847295864263</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>15</v>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117">
+        <v>8.48356309650053e-05</v>
+      </c>
+      <c r="D117">
+        <v>0.998557794273595</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>15.5</v>
+      </c>
+      <c r="B118">
+        <v>4</v>
+      </c>
+      <c r="C118">
+        <v>0.000169671261930011</v>
+      </c>
+      <c r="D118">
+        <v>0.998727465535525</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>16</v>
+      </c>
+      <c r="B119">
+        <v>3</v>
+      </c>
+      <c r="C119">
+        <v>0.000127253446447508</v>
+      </c>
+      <c r="D119">
+        <v>0.998854718981972</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>16.5</v>
+      </c>
+      <c r="B120">
+        <v>5</v>
+      </c>
+      <c r="C120">
+        <v>0.000212089077412513</v>
+      </c>
+      <c r="D120">
+        <v>0.999066808059385</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>17</v>
+      </c>
+      <c r="B121">
+        <v>3</v>
+      </c>
+      <c r="C121">
+        <v>0.000127253446447508</v>
+      </c>
+      <c r="D121">
+        <v>0.999194061505832</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>17.5</v>
+      </c>
+      <c r="B122">
+        <v>3</v>
+      </c>
+      <c r="C122">
+        <v>0.000127253446447508</v>
+      </c>
+      <c r="D122">
+        <v>0.99932131495228</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>18</v>
+      </c>
+      <c r="B123">
+        <v>3</v>
+      </c>
+      <c r="C123">
+        <v>0.000127253446447508</v>
+      </c>
+      <c r="D123">
+        <v>0.999448568398727</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>18.5</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>8.48356309650053e-05</v>
+      </c>
+      <c r="D124">
+        <v>0.999533404029692</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>19</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>4.24178154825026e-05</v>
+      </c>
+      <c r="D125">
+        <v>0.999575821845175</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>20</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>4.24178154825026e-05</v>
+      </c>
+      <c r="D126">
+        <v>0.999618239660657</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>20.5</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>4.24178154825026e-05</v>
+      </c>
+      <c r="D127">
+        <v>0.99966065747614</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>21</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128">
+        <v>0.000127253446447508</v>
+      </c>
+      <c r="D128">
+        <v>0.999787910922587</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>21.5</v>
+      </c>
+      <c r="B129">
+        <v>3</v>
+      </c>
+      <c r="C129">
+        <v>0.000127253446447508</v>
+      </c>
+      <c r="D129">
+        <v>0.999915164369035</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>23.5</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>4.24178154825026e-05</v>
+      </c>
+      <c r="D130">
+        <v>0.999957582184517</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>24.5</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>4.24178154825026e-05</v>
+      </c>
+      <c r="D131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>145355</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>0.721354630105552</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.288201028697444</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>0.05</v>
+      </c>
+      <c r="B146">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>0.1</v>
+      </c>
+      <c r="B147">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>0.15</v>
+      </c>
+      <c r="B148">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>0.2</v>
+      </c>
+      <c r="B149">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>0.25</v>
+      </c>
+      <c r="B150">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>0.3</v>
+      </c>
+      <c r="B151">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>0.35</v>
+      </c>
+      <c r="B152">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>0.4</v>
+      </c>
+      <c r="B153">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0.45</v>
+      </c>
+      <c r="B154">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>0.5</v>
+      </c>
+      <c r="B155">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>0.55</v>
+      </c>
+      <c r="B156">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>0.6</v>
+      </c>
+      <c r="B157">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>0.65</v>
+      </c>
+      <c r="B158">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>0.7</v>
+      </c>
+      <c r="B159">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>0.75</v>
+      </c>
+      <c r="B160">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>0.8</v>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>0.85</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>0.9</v>
+      </c>
+      <c r="B163">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>0.95</v>
+      </c>
+      <c r="B164">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>0.5</v>
+      </c>
+      <c r="B166">
+        <v>70890</v>
+      </c>
+      <c r="C166">
+        <v>0.487702521413092</v>
+      </c>
+      <c r="D166">
+        <v>0.487702521413092</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B167">
+        <v>31482</v>
+      </c>
+      <c r="C167">
+        <v>0.216586976712187</v>
+      </c>
+      <c r="D167">
+        <v>0.70428949812528</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B168">
+        <v>12131</v>
+      </c>
+      <c r="C168">
+        <v>0.083457741391765</v>
+      </c>
+      <c r="D168">
+        <v>0.787747239517045</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>1</v>
+      </c>
+      <c r="B169">
+        <v>9061</v>
+      </c>
+      <c r="C169">
+        <v>0.062337036909635</v>
+      </c>
+      <c r="D169">
+        <v>0.850084276426679</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B170">
+        <v>11637</v>
+      </c>
+      <c r="C170">
+        <v>0.0800591654913832</v>
+      </c>
+      <c r="D170">
+        <v>0.930143441918063</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B171">
+        <v>3861</v>
+      </c>
+      <c r="C171">
+        <v>0.0265625537477211</v>
+      </c>
+      <c r="D171">
+        <v>0.956705995665784</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B172">
+        <v>2775</v>
+      </c>
+      <c r="C172">
+        <v>0.0190911905335214</v>
+      </c>
+      <c r="D172">
+        <v>0.975797186199305</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>1.5</v>
+      </c>
+      <c r="B173">
+        <v>1637</v>
+      </c>
+      <c r="C173">
+        <v>0.0112620824877025</v>
+      </c>
+      <c r="D173">
+        <v>0.987059268687008</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B174">
+        <v>470</v>
+      </c>
+      <c r="C174">
+        <v>0.00323346290117299</v>
+      </c>
+      <c r="D174">
+        <v>0.990292731588181</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B175">
+        <v>323</v>
+      </c>
+      <c r="C175">
+        <v>0.00222214578101889</v>
+      </c>
+      <c r="D175">
+        <v>0.9925148773692</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B176">
+        <v>151</v>
+      </c>
+      <c r="C176">
+        <v>0.00103883595335558</v>
+      </c>
+      <c r="D176">
+        <v>0.993553713322555</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B177">
+        <v>218</v>
+      </c>
+      <c r="C177">
+        <v>0.00149977640948024</v>
+      </c>
+      <c r="D177">
+        <v>0.995053489732035</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B178">
+        <v>245</v>
+      </c>
+      <c r="C178">
+        <v>0.00168552853359018</v>
+      </c>
+      <c r="D178">
+        <v>0.996739018265625</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2</v>
+      </c>
+      <c r="B179">
+        <v>23</v>
+      </c>
+      <c r="C179">
+        <v>0.000158233290908465</v>
+      </c>
+      <c r="D179">
+        <v>0.996897251556534</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B180">
+        <v>126</v>
+      </c>
+      <c r="C180">
+        <v>0.000866843245846376</v>
+      </c>
+      <c r="D180">
+        <v>0.99776409480238</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B181">
+        <v>70</v>
+      </c>
+      <c r="C181">
+        <v>0.000481579581025764</v>
+      </c>
+      <c r="D181">
+        <v>0.998245674383406</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B182">
+        <v>38</v>
+      </c>
+      <c r="C182">
+        <v>0.000261428915413986</v>
+      </c>
+      <c r="D182">
+        <v>0.99850710329882</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B183">
+        <v>28</v>
+      </c>
+      <c r="C183">
+        <v>0.000192631832410306</v>
+      </c>
+      <c r="D183">
+        <v>0.99869973513123</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B184">
+        <v>51</v>
+      </c>
+      <c r="C184">
+        <v>0.000350865123318771</v>
+      </c>
+      <c r="D184">
+        <v>0.999050600254549</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B185">
+        <v>26</v>
+      </c>
+      <c r="C185">
+        <v>0.00017887241580957</v>
+      </c>
+      <c r="D185">
+        <v>0.999229472670359</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B186">
+        <v>17</v>
+      </c>
+      <c r="C186">
+        <v>0.000116955041106257</v>
+      </c>
+      <c r="D186">
+        <v>0.999346427711465</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>2.5</v>
+      </c>
+      <c r="B187">
+        <v>21</v>
+      </c>
+      <c r="C187">
+        <v>0.000144473874307729</v>
+      </c>
+      <c r="D187">
+        <v>0.999490901585773</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B188">
+        <v>32</v>
+      </c>
+      <c r="C188">
+        <v>0.000220150665611778</v>
+      </c>
+      <c r="D188">
+        <v>0.999711052251385</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B189">
+        <v>7</v>
+      </c>
+      <c r="C189">
+        <v>4.81579581025764e-05</v>
+      </c>
+      <c r="D189">
+        <v>0.999759210209487</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B190">
+        <v>16</v>
+      </c>
+      <c r="C190">
+        <v>0.000110075332805889</v>
+      </c>
+      <c r="D190">
+        <v>0.999869285542293</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B191">
+        <v>5</v>
+      </c>
+      <c r="C191">
+        <v>3.43985415018403e-05</v>
+      </c>
+      <c r="D191">
+        <v>0.999903684083795</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B192">
+        <v>3</v>
+      </c>
+      <c r="C192">
+        <v>2.06391249011042e-05</v>
+      </c>
+      <c r="D192">
+        <v>0.999924323208696</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B193">
+        <v>6</v>
+      </c>
+      <c r="C193">
+        <v>4.12782498022084e-05</v>
+      </c>
+      <c r="D193">
+        <v>0.999965601458498</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B194">
+        <v>3</v>
+      </c>
+      <c r="C194">
+        <v>2.06391249011042e-05</v>
+      </c>
+      <c r="D194">
+        <v>0.999986240583399</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+      <c r="C195">
+        <v>6.87970830036806e-06</v>
+      </c>
+      <c r="D195">
+        <v>0.9999931202917</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B196">
+        <v>1</v>
+      </c>
+      <c r="C196">
+        <v>6.87970830036806e-06</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197"/>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B202">
+        <v>0.445514678955078</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B203">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>0</v>
+      </c>
+      <c r="B208">
+        <v>0.445514678955078</v>
+      </c>
+      <c r="C208">
+        <v>1</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>0.5</v>
+      </c>
+      <c r="B209">
+        <v>0.357030232747396</v>
+      </c>
+      <c r="C209">
+        <v>6</v>
+      </c>
+      <c r="D209">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>1</v>
+      </c>
+      <c r="B210">
+        <v>0.314618624173678</v>
+      </c>
+      <c r="C210">
+        <v>26</v>
+      </c>
+      <c r="D210">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>1.5</v>
+      </c>
+      <c r="B211">
+        <v>0.264440409342448</v>
+      </c>
+      <c r="C211">
+        <v>90</v>
+      </c>
+      <c r="D211">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>2</v>
+      </c>
+      <c r="B212">
+        <v>0.232952004048362</v>
+      </c>
+      <c r="C212">
+        <v>134</v>
+      </c>
+      <c r="D212">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>2.5</v>
+      </c>
+      <c r="B213">
+        <v>0.213329699612403</v>
+      </c>
+      <c r="C213">
+        <v>258</v>
+      </c>
+      <c r="D213">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>3</v>
+      </c>
+      <c r="B214">
+        <v>0.205734141280011</v>
+      </c>
+      <c r="C214">
+        <v>410</v>
+      </c>
+      <c r="D214">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>3.5</v>
+      </c>
+      <c r="B215">
+        <v>0.20567890120904</v>
+      </c>
+      <c r="C215">
+        <v>494</v>
+      </c>
+      <c r="D215">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>4</v>
+      </c>
+      <c r="B216">
+        <v>0.207105907495471</v>
+      </c>
+      <c r="C216">
+        <v>690</v>
+      </c>
+      <c r="D216">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>4.5</v>
+      </c>
+      <c r="B217">
+        <v>0.206903001622698</v>
+      </c>
+      <c r="C217">
+        <v>962</v>
+      </c>
+      <c r="D217">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>5</v>
+      </c>
+      <c r="B218">
+        <v>0.205273821054261</v>
+      </c>
+      <c r="C218">
+        <v>1098</v>
+      </c>
+      <c r="D218">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>5.5</v>
+      </c>
+      <c r="B219">
+        <v>0.203710200606844</v>
+      </c>
+      <c r="C219">
+        <v>1406</v>
+      </c>
+      <c r="D219">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>6</v>
+      </c>
+      <c r="B220">
+        <v>0.202666573953568</v>
+      </c>
+      <c r="C220">
+        <v>1578</v>
+      </c>
+      <c r="D220">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>6.5</v>
+      </c>
+      <c r="B221">
+        <v>0.201943570487681</v>
+      </c>
+      <c r="C221">
+        <v>2018</v>
+      </c>
+      <c r="D221">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>7</v>
+      </c>
+      <c r="B222">
+        <v>0.201298492978924</v>
+      </c>
+      <c r="C222">
+        <v>2342</v>
+      </c>
+      <c r="D222">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>7.5</v>
+      </c>
+      <c r="B223">
+        <v>0.20064738453928</v>
+      </c>
+      <c r="C223">
+        <v>2634</v>
+      </c>
+      <c r="D223">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>8</v>
+      </c>
+      <c r="B224">
+        <v>0.200110410097923</v>
+      </c>
+      <c r="C224">
+        <v>2930</v>
+      </c>
+      <c r="D224">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>8.5</v>
+      </c>
+      <c r="B225">
+        <v>0.199702288107897</v>
+      </c>
+      <c r="C225">
+        <v>3402</v>
+      </c>
+      <c r="D225">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>9</v>
+      </c>
+      <c r="B226">
+        <v>0.199361945923287</v>
+      </c>
+      <c r="C226">
+        <v>3926</v>
+      </c>
+      <c r="D226">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>9.5</v>
+      </c>
+      <c r="B227">
+        <v>0.199203621765509</v>
+      </c>
+      <c r="C227">
+        <v>4266</v>
+      </c>
+      <c r="D227">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>10</v>
+      </c>
+      <c r="B228">
+        <v>0.198968947815845</v>
+      </c>
+      <c r="C228">
+        <v>4730</v>
+      </c>
+      <c r="D228">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>10.5</v>
+      </c>
+      <c r="B229">
+        <v>0.198749560236715</v>
+      </c>
+      <c r="C229">
+        <v>5510</v>
+      </c>
+      <c r="D229">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>11</v>
+      </c>
+      <c r="B230">
+        <v>0.198531281472281</v>
+      </c>
+      <c r="C230">
+        <v>5562</v>
+      </c>
+      <c r="D230">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>11.5</v>
+      </c>
+      <c r="B231">
+        <v>0.198303935605911</v>
+      </c>
+      <c r="C231">
+        <v>6410</v>
+      </c>
+      <c r="D231">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>12</v>
+      </c>
+      <c r="B232">
+        <v>0.198053133670994</v>
+      </c>
+      <c r="C232">
+        <v>6894</v>
+      </c>
+      <c r="D232">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>12.5</v>
+      </c>
+      <c r="B233">
+        <v>0.197838642441224</v>
+      </c>
+      <c r="C233">
+        <v>7490</v>
+      </c>
+      <c r="D233">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>13</v>
+      </c>
+      <c r="B234">
+        <v>0.197656485958751</v>
+      </c>
+      <c r="C234">
+        <v>8258</v>
+      </c>
+      <c r="D234">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>13.5</v>
+      </c>
+      <c r="B235">
+        <v>0.197586841680804</v>
+      </c>
+      <c r="C235">
+        <v>8994</v>
+      </c>
+      <c r="D235">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>14</v>
+      </c>
+      <c r="B236">
+        <v>0.197662043364503</v>
+      </c>
+      <c r="C236">
+        <v>9446</v>
+      </c>
+      <c r="D236">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>14.5</v>
+      </c>
+      <c r="B237">
+        <v>0.197793524354654</v>
+      </c>
+      <c r="C237">
+        <v>9978</v>
+      </c>
+      <c r="D237">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>15</v>
+      </c>
+      <c r="B238">
+        <v>0.197926164251359</v>
+      </c>
+      <c r="C238">
+        <v>11138</v>
+      </c>
+      <c r="D238">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>15.5</v>
+      </c>
+      <c r="B239">
+        <v>0.197960593544473</v>
+      </c>
+      <c r="C239">
+        <v>11406</v>
+      </c>
+      <c r="D239">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>16</v>
+      </c>
+      <c r="B240">
+        <v>0.197986671644935</v>
+      </c>
+      <c r="C240">
+        <v>12575</v>
+      </c>
+      <c r="D240">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>16.5</v>
+      </c>
+      <c r="B241">
+        <v>0.197978685979974</v>
+      </c>
+      <c r="C241">
+        <v>12848</v>
+      </c>
+      <c r="D241">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>17</v>
+      </c>
+      <c r="B242">
+        <v>0.197948000324306</v>
+      </c>
+      <c r="C242">
+        <v>12060</v>
+      </c>
+      <c r="D242">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>17.5</v>
+      </c>
+      <c r="B243">
+        <v>0.197924515385823</v>
+      </c>
+      <c r="C243">
+        <v>11804</v>
+      </c>
+      <c r="D243">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>18</v>
+      </c>
+      <c r="B244">
+        <v>0.197927797022468</v>
+      </c>
+      <c r="C244">
+        <v>11016</v>
+      </c>
+      <c r="D244">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>18.5</v>
+      </c>
+      <c r="B245">
+        <v>0.198019814179322</v>
+      </c>
+      <c r="C245">
+        <v>10700</v>
+      </c>
+      <c r="D245">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>19</v>
+      </c>
+      <c r="B246">
+        <v>0.198088063720603</v>
+      </c>
+      <c r="C246">
+        <v>9756</v>
+      </c>
+      <c r="D246">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>19.5</v>
+      </c>
+      <c r="B247">
+        <v>0.198181470786605</v>
+      </c>
+      <c r="C247">
+        <v>9224</v>
+      </c>
+      <c r="D247">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>20</v>
+      </c>
+      <c r="B248">
+        <v>0.198249098236055</v>
+      </c>
+      <c r="C248">
+        <v>8408</v>
+      </c>
+      <c r="D248">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>20.5</v>
+      </c>
+      <c r="B249">
+        <v>0.19827873426551</v>
+      </c>
+      <c r="C249">
+        <v>7452</v>
+      </c>
+      <c r="D249">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>21</v>
+      </c>
+      <c r="B250">
+        <v>0.198246981880882</v>
+      </c>
+      <c r="C250">
+        <v>7040</v>
+      </c>
+      <c r="D250">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>21.5</v>
+      </c>
+      <c r="B251">
+        <v>0.198261959692047</v>
+      </c>
+      <c r="C251">
+        <v>5820</v>
+      </c>
+      <c r="D251">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>22</v>
+      </c>
+      <c r="B252">
+        <v>0.198375644058478</v>
+      </c>
+      <c r="C252">
+        <v>4880</v>
+      </c>
+      <c r="D252">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>22.5</v>
+      </c>
+      <c r="B253">
+        <v>0.198490104055017</v>
+      </c>
+      <c r="C253">
+        <v>3936</v>
+      </c>
+      <c r="D253">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>23</v>
+      </c>
+      <c r="B254">
+        <v>0.198635196717591</v>
+      </c>
+      <c r="C254">
+        <v>2999</v>
+      </c>
+      <c r="D254">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>23.5</v>
+      </c>
+      <c r="B255">
+        <v>0.198703027427743</v>
+      </c>
+      <c r="C255">
+        <v>2180</v>
+      </c>
+      <c r="D255">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>24</v>
+      </c>
+      <c r="B256">
+        <v>0.198727318092629</v>
+      </c>
+      <c r="C256">
+        <v>1620</v>
+      </c>
+      <c r="D256">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>24.5</v>
+      </c>
+      <c r="B257">
+        <v>0.198677037725385</v>
+      </c>
+      <c r="C257">
+        <v>1208</v>
+      </c>
+      <c r="D257">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>25</v>
+      </c>
+      <c r="B258">
+        <v>0.198843783886822</v>
+      </c>
+      <c r="C258">
+        <v>942</v>
+      </c>
+      <c r="D258">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>25.5</v>
+      </c>
+      <c r="B259">
+        <v>0.198901176452637</v>
+      </c>
+      <c r="C259">
+        <v>584</v>
+      </c>
+      <c r="D259">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>26</v>
+      </c>
+      <c r="B260">
+        <v>0.198602703255667</v>
+      </c>
+      <c r="C260">
+        <v>284</v>
+      </c>
+      <c r="D260">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>26.5</v>
+      </c>
+      <c r="B261">
+        <v>0.198047439257304</v>
+      </c>
+      <c r="C261">
+        <v>192</v>
+      </c>
+      <c r="D261">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>27</v>
+      </c>
+      <c r="B262">
+        <v>0.19629141000601</v>
+      </c>
+      <c r="C262">
+        <v>104</v>
+      </c>
+      <c r="D262">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>27.5</v>
+      </c>
+      <c r="B263">
+        <v>0.1942351659139</v>
+      </c>
+      <c r="C263">
+        <v>24</v>
+      </c>
+      <c r="D263">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>28</v>
+      </c>
+      <c r="B264">
+        <v>0.192596435546875</v>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+      <c r="D264">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>0</v>
+      </c>
+      <c r="B266">
+        <v>0.445514678955078</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>0.5</v>
+      </c>
+      <c r="B267">
+        <v>0.355583190917969</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>1</v>
+      </c>
+      <c r="B268">
+        <v>0.293132781982422</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>1.5</v>
+      </c>
+      <c r="B269">
+        <v>0.245002746582031</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>2</v>
+      </c>
+      <c r="B270">
+        <v>0.221717834472656</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>2.5</v>
+      </c>
+      <c r="B271">
+        <v>0.202476501464844</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>3</v>
+      </c>
+      <c r="B272">
+        <v>0.204681396484375</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>3.5</v>
+      </c>
+      <c r="B273">
+        <v>0.202869415283203</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>4</v>
+      </c>
+      <c r="B274">
+        <v>0.204898834228516</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>4.5</v>
+      </c>
+      <c r="B275">
+        <v>0.204158782958984</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>5</v>
+      </c>
+      <c r="B276">
+        <v>0.202415466308594</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>5.5</v>
+      </c>
+      <c r="B277">
+        <v>0.200809478759766</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>6</v>
+      </c>
+      <c r="B278">
+        <v>0.20013427734375</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>6.5</v>
+      </c>
+      <c r="B279">
+        <v>0.200359344482422</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>7</v>
+      </c>
+      <c r="B280">
+        <v>0.200832366943359</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>7.5</v>
+      </c>
+      <c r="B281">
+        <v>0.201091766357422</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>8</v>
+      </c>
+      <c r="B282">
+        <v>0.201683044433594</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>8.5</v>
+      </c>
+      <c r="B283">
+        <v>0.201557159423828</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>9</v>
+      </c>
+      <c r="B284">
+        <v>0.201141357421875</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>9.5</v>
+      </c>
+      <c r="B285">
+        <v>0.20098876953125</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>10</v>
+      </c>
+      <c r="B286">
+        <v>0.2010498046875</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>10.5</v>
+      </c>
+      <c r="B287">
+        <v>0.201065063476562</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>11</v>
+      </c>
+      <c r="B288">
+        <v>0.200294494628906</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>11.5</v>
+      </c>
+      <c r="B289">
+        <v>0.199535369873047</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>12</v>
+      </c>
+      <c r="B290">
+        <v>0.198661804199219</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>12.5</v>
+      </c>
+      <c r="B291">
+        <v>0.198711395263672</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>13</v>
+      </c>
+      <c r="B292">
+        <v>0.199558258056641</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>13.5</v>
+      </c>
+      <c r="B293">
+        <v>0.200572967529297</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>14</v>
+      </c>
+      <c r="B294">
+        <v>0.201118469238281</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>14.5</v>
+      </c>
+      <c r="B295">
+        <v>0.201652526855469</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>15</v>
+      </c>
+      <c r="B296">
+        <v>0.201889038085938</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>15.5</v>
+      </c>
+      <c r="B297">
+        <v>0.201850891113281</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>16</v>
+      </c>
+      <c r="B298">
+        <v>0.201248168945312</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>0</v>
+      </c>
+      <c r="B300">
+        <v>0.445514678955078</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>0.5</v>
+      </c>
+      <c r="B301">
+        <v>0.357944488525391</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>1</v>
+      </c>
+      <c r="B302">
+        <v>0.295970916748047</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>1.5</v>
+      </c>
+      <c r="B303">
+        <v>0.249702453613281</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>2</v>
+      </c>
+      <c r="B304">
+        <v>0.226398468017578</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>2.5</v>
+      </c>
+      <c r="B305">
+        <v>0.208927154541016</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>3</v>
+      </c>
+      <c r="B306">
+        <v>0.211475372314453</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>3.5</v>
+      </c>
+      <c r="B307">
+        <v>0.210403442382812</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>4</v>
+      </c>
+      <c r="B308">
+        <v>0.212093353271484</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>4.5</v>
+      </c>
+      <c r="B309">
+        <v>0.210262298583984</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>5</v>
+      </c>
+      <c r="B310">
+        <v>0.207515716552734</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>5.5</v>
+      </c>
+      <c r="B311">
+        <v>0.205276489257812</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>6</v>
+      </c>
+      <c r="B312">
+        <v>0.203971862792969</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>6.5</v>
+      </c>
+      <c r="B313">
+        <v>0.202980041503906</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>7</v>
+      </c>
+      <c r="B314">
+        <v>0.202194213867188</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>7.5</v>
+      </c>
+      <c r="B315">
+        <v>0.201194763183594</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>8</v>
+      </c>
+      <c r="B316">
+        <v>0.200180053710938</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>8.5</v>
+      </c>
+      <c r="B317">
+        <v>0.199542999267578</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>9</v>
+      </c>
+      <c r="B318">
+        <v>0.198276519775391</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>9.5</v>
+      </c>
+      <c r="B319">
+        <v>0.197364807128906</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>10</v>
+      </c>
+      <c r="B320">
+        <v>0.196815490722656</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>10.5</v>
+      </c>
+      <c r="B321">
+        <v>0.197536468505859</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>11</v>
+      </c>
+      <c r="B322">
+        <v>0.198249816894531</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>11.5</v>
+      </c>
+      <c r="B323">
+        <v>0.198890686035156</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>12</v>
+      </c>
+      <c r="B324">
+        <v>0.199424743652344</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>12.5</v>
+      </c>
+      <c r="B325">
+        <v>0.200042724609375</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>13</v>
+      </c>
+      <c r="B326">
+        <v>0.199913024902344</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>13.5</v>
+      </c>
+      <c r="B327">
+        <v>0.199470520019531</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>14</v>
+      </c>
+      <c r="B328">
+        <v>0.198833465576172</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>14.5</v>
+      </c>
+      <c r="B329">
+        <v>0.197803497314453</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>15</v>
+      </c>
+      <c r="B330">
+        <v>0.196521759033203</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>15.5</v>
+      </c>
+      <c r="B331">
+        <v>0.195854187011719</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>16</v>
+      </c>
+      <c r="B332">
+        <v>0.195632934570312</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>0</v>
+      </c>
+      <c r="B334">
+        <v>0.445514678955078</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>0.5</v>
+      </c>
+      <c r="B335">
+        <v>0.357563018798828</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>1</v>
+      </c>
+      <c r="B336">
+        <v>0.295536041259766</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>1.5</v>
+      </c>
+      <c r="B337">
+        <v>0.248420715332031</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>2</v>
+      </c>
+      <c r="B338">
+        <v>0.223766326904297</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>2.5</v>
+      </c>
+      <c r="B339">
+        <v>0.205211639404297</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>3</v>
+      </c>
+      <c r="B340">
+        <v>0.206424713134766</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>3.5</v>
+      </c>
+      <c r="B341">
+        <v>0.204303741455078</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>4</v>
+      </c>
+      <c r="B342">
+        <v>0.20611572265625</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>4.5</v>
+      </c>
+      <c r="B343">
+        <v>0.205036163330078</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>5</v>
+      </c>
+      <c r="B344">
+        <v>0.204071044921875</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>5.5</v>
+      </c>
+      <c r="B345">
+        <v>0.203380584716797</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>6</v>
+      </c>
+      <c r="B346">
+        <v>0.203716278076172</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>6.5</v>
+      </c>
+      <c r="B347">
+        <v>0.203380584716797</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>7</v>
+      </c>
+      <c r="B348">
+        <v>0.202178955078125</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>7.5</v>
+      </c>
+      <c r="B349">
+        <v>0.200572967529297</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>8</v>
+      </c>
+      <c r="B350">
+        <v>0.199703216552734</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>8.5</v>
+      </c>
+      <c r="B351">
+        <v>0.199851989746094</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>9</v>
+      </c>
+      <c r="B352">
+        <v>0.200412750244141</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>9.5</v>
+      </c>
+      <c r="B353">
+        <v>0.200839996337891</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>10</v>
+      </c>
+      <c r="B354">
+        <v>0.201091766357422</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>10.5</v>
+      </c>
+      <c r="B355">
+        <v>0.201473236083984</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>11</v>
+      </c>
+      <c r="B356">
+        <v>0.201858520507812</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>11.5</v>
+      </c>
+      <c r="B357">
+        <v>0.201629638671875</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>12</v>
+      </c>
+      <c r="B358">
+        <v>0.200923919677734</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>12.5</v>
+      </c>
+      <c r="B359">
+        <v>0.199741363525391</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>13</v>
+      </c>
+      <c r="B360">
+        <v>0.198894500732422</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>13.5</v>
+      </c>
+      <c r="B361">
+        <v>0.197650909423828</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>14</v>
+      </c>
+      <c r="B362">
+        <v>0.196865081787109</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>14.5</v>
+      </c>
+      <c r="B363">
+        <v>0.196319580078125</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>15</v>
+      </c>
+      <c r="B364">
+        <v>0.196216583251953</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>15.5</v>
+      </c>
+      <c r="B365">
+        <v>0.195598602294922</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>16</v>
+      </c>
+      <c r="B366">
+        <v>0.195358276367187</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>